--- a/data/trans_orig/P79A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>21375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>30153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>628918</t>
+          <t>682799</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621282</t>
+          <t>675840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632695</t>
+          <t>687362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>716636</t>
+          <t>722774</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>710799</t>
+          <t>712805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>720769</t>
+          <t>727483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1345555</t>
+          <t>1405572</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1337309</t>
+          <t>1394736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1351595</t>
+          <t>1413211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>22711</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36390</t>
+          <t>40197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>33652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>61183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1174059</t>
+          <t>1026206</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1156474</t>
+          <t>1008720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1185186</t>
+          <t>1036084</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>941186</t>
+          <t>1051898</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928065</t>
+          <t>1037822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>948401</t>
+          <t>1059884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2115246</t>
+          <t>2078104</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2096977</t>
+          <t>2059208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2129226</t>
+          <t>2091393</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>28983</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40996</t>
+          <t>49006</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>31565</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62280</t>
+          <t>65661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>680501</t>
+          <t>774090</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663684</t>
+          <t>754067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>690300</t>
+          <t>786403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>918162</t>
+          <t>797142</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>899496</t>
+          <t>785285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>927397</t>
+          <t>803056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1598663</t>
+          <t>1571231</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1575766</t>
+          <t>1549671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1613558</t>
+          <t>1583767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31753</t>
+          <t>37342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32837</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21752</t>
+          <t>27056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45705</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54482</t>
+          <t>63936</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41598</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>81225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>905186</t>
+          <t>964306</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895078</t>
+          <t>952720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913188</t>
+          <t>973251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1062095</t>
+          <t>1080861</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1049227</t>
+          <t>1067188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1073180</t>
+          <t>1091985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1967281</t>
+          <t>2045168</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1949715</t>
+          <t>2027879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1980165</t>
+          <t>2060460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95956</t>
+          <t>111769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54238</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95737</t>
+          <t>106853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115676</t>
+          <t>141286</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>180662</t>
+          <t>202044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3388664</t>
+          <t>3447400</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3363861</t>
+          <t>3420993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3408036</t>
+          <t>3466301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3638081</t>
+          <t>3652675</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3616543</t>
+          <t>3630101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3658042</t>
+          <t>3669368</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7026745</t>
+          <t>7100075</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6991435</t>
+          <t>7067672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7056421</t>
+          <t>7128430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
